--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N23_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H27"/>
+  <dimension ref="A1:H28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,10 +486,10 @@
         <v>55.29136996492917</v>
       </c>
       <c r="E2" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F2" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -518,10 +518,10 @@
         <v>44.39408360775397</v>
       </c>
       <c r="E3" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F3" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
         <v>48.13047981793661</v>
       </c>
       <c r="E4" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F4" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -582,10 +582,10 @@
         <v>62.72190236805042</v>
       </c>
       <c r="E5" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F5" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -614,10 +614,10 @@
         <v>74.69571558960243</v>
       </c>
       <c r="E6" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F6" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -646,10 +646,10 @@
         <v>44.25833266467649</v>
       </c>
       <c r="E7" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F7" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -678,10 +678,10 @@
         <v>56.12488827529006</v>
       </c>
       <c r="E8" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F8" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         <v>24.2447207347794</v>
       </c>
       <c r="E9" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F9" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -742,10 +742,10 @@
         <v>49.08315781173381</v>
       </c>
       <c r="E10" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F10" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         <v>46.51061315020947</v>
       </c>
       <c r="E11" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F11" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -806,10 +806,10 @@
         <v>25.79686390036104</v>
       </c>
       <c r="E12" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F12" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -838,10 +838,10 @@
         <v>8.335814302678907</v>
       </c>
       <c r="E13" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F13" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -870,10 +870,10 @@
         <v>29.65062544887669</v>
       </c>
       <c r="E14" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F14" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -902,10 +902,10 @@
         <v>46.13298141141758</v>
       </c>
       <c r="E15" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F15" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>60.42029276989749</v>
       </c>
       <c r="E16" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F16" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
         <v>10.66727946879847</v>
       </c>
       <c r="E17" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F17" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -998,10 +998,10 @@
         <v>38.38283418964885</v>
       </c>
       <c r="E18" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F18" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
         <v>56.24362671983853</v>
       </c>
       <c r="E19" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F19" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1062,10 +1062,10 @@
         <v>44.31413414801926</v>
       </c>
       <c r="E20" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F20" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         <v>27.07416023319651</v>
       </c>
       <c r="E21" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F21" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1126,10 +1126,10 @@
         <v>58.07968489676145</v>
       </c>
       <c r="E22" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F22" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         <v>65.20928033771415</v>
       </c>
       <c r="E23" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F23" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1190,10 +1190,10 @@
         <v>45.44222496739781</v>
       </c>
       <c r="E24" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F24" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1222,10 +1222,10 @@
         <v>44.6492810907766</v>
       </c>
       <c r="E25" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F25" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1254,10 +1254,10 @@
         <v>68.72104849642652</v>
       </c>
       <c r="E26" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F26" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1286,10 +1286,10 @@
         <v>60.25013967958422</v>
       </c>
       <c r="E27" t="n">
-        <v>16.50551278757331</v>
+        <v>16.25837087782054</v>
       </c>
       <c r="F27" t="n">
-        <v>16.52019200788393</v>
+        <v>16.27734277328756</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1297,6 +1297,38 @@
         </is>
       </c>
       <c r="H27" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>W0045F0002T0006Z000C1N23.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>27</v>
+      </c>
+      <c r="C28" t="n">
+        <v>38.48345284238166</v>
+      </c>
+      <c r="D28" t="n">
+        <v>38.20297517053401</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.25837087782054</v>
+      </c>
+      <c r="F28" t="n">
+        <v>16.27734277328756</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>T6758</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N23_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6758_W0045F0002T0006Z000C1N23_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>54.9593423260036</v>
+        <v>8.930893127975585</v>
       </c>
       <c r="D2" t="n">
-        <v>55.29136996492917</v>
+        <v>8.984847619300991</v>
       </c>
       <c r="E2" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F2" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.07196156602085</v>
+        <v>7.161693754478389</v>
       </c>
       <c r="D3" t="n">
-        <v>44.39408360775397</v>
+        <v>7.21403858626002</v>
       </c>
       <c r="E3" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F3" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.78741799518676</v>
+        <v>7.76545542421785</v>
       </c>
       <c r="D4" t="n">
-        <v>48.13047981793661</v>
+        <v>7.821202970414699</v>
       </c>
       <c r="E4" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F4" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.43803727570518</v>
+        <v>10.14618105730209</v>
       </c>
       <c r="D5" t="n">
-        <v>62.72190236805042</v>
+        <v>10.19230913480819</v>
       </c>
       <c r="E5" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F5" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>74.46009820409569</v>
+        <v>12.09976595816555</v>
       </c>
       <c r="D6" t="n">
-        <v>74.69571558960243</v>
+        <v>12.1380537833104</v>
       </c>
       <c r="E6" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F6" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.96688763590593</v>
+        <v>7.144619240834714</v>
       </c>
       <c r="D7" t="n">
-        <v>44.25833266467649</v>
+        <v>7.191979058009931</v>
       </c>
       <c r="E7" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F7" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>56.00435652226535</v>
+        <v>9.100707934868119</v>
       </c>
       <c r="D8" t="n">
-        <v>56.12488827529006</v>
+        <v>9.120294344734635</v>
       </c>
       <c r="E8" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F8" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>23.95743726068022</v>
+        <v>3.893083554860535</v>
       </c>
       <c r="D9" t="n">
-        <v>24.2447207347794</v>
+        <v>3.939767119401652</v>
       </c>
       <c r="E9" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F9" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>48.92191697275884</v>
+        <v>7.949811508073313</v>
       </c>
       <c r="D10" t="n">
-        <v>49.08315781173381</v>
+        <v>7.976013144406743</v>
       </c>
       <c r="E10" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F10" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>46.40888526564433</v>
+        <v>7.541443855667204</v>
       </c>
       <c r="D11" t="n">
-        <v>46.51061315020947</v>
+        <v>7.55797463690904</v>
       </c>
       <c r="E11" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F11" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>25.75228231183805</v>
+        <v>4.184745875673683</v>
       </c>
       <c r="D12" t="n">
-        <v>25.79686390036104</v>
+        <v>4.19199038380867</v>
       </c>
       <c r="E12" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F12" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>8.25033253971492</v>
+        <v>1.340679037703675</v>
       </c>
       <c r="D13" t="n">
-        <v>8.335814302678907</v>
+        <v>1.354569824185322</v>
       </c>
       <c r="E13" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F13" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>29.69058271154549</v>
+        <v>4.824719690626142</v>
       </c>
       <c r="D14" t="n">
-        <v>29.65062544887669</v>
+        <v>4.818226635442462</v>
       </c>
       <c r="E14" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F14" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>46.2407673072148</v>
+        <v>7.514124687422406</v>
       </c>
       <c r="D15" t="n">
-        <v>46.13298141141758</v>
+        <v>7.496609479355357</v>
       </c>
       <c r="E15" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F15" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>60.51155984645605</v>
+        <v>9.833128475049108</v>
       </c>
       <c r="D16" t="n">
-        <v>60.42029276989749</v>
+        <v>9.818297575108343</v>
       </c>
       <c r="E16" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F16" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>10.96507575503765</v>
+        <v>1.781824810193618</v>
       </c>
       <c r="D17" t="n">
-        <v>10.66727946879847</v>
+        <v>1.733432913679751</v>
       </c>
       <c r="E17" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F17" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>38.48569111171781</v>
+        <v>6.253924805654144</v>
       </c>
       <c r="D18" t="n">
-        <v>38.38283418964885</v>
+        <v>6.237210555817938</v>
       </c>
       <c r="E18" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F18" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>56.34145824118057</v>
+        <v>9.155486964191843</v>
       </c>
       <c r="D19" t="n">
-        <v>56.24362671983853</v>
+        <v>9.139589341973762</v>
       </c>
       <c r="E19" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F19" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>44.51765733254494</v>
+        <v>7.234119316538552</v>
       </c>
       <c r="D20" t="n">
-        <v>44.31413414801926</v>
+        <v>7.201046799053129</v>
       </c>
       <c r="E20" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F20" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>27.37690807171375</v>
+        <v>4.448747561653485</v>
       </c>
       <c r="D21" t="n">
-        <v>27.07416023319651</v>
+        <v>4.399551037894433</v>
       </c>
       <c r="E21" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F21" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>58.27126910299075</v>
+        <v>9.469081229235996</v>
       </c>
       <c r="D22" t="n">
-        <v>58.07968489676145</v>
+        <v>9.437948795723736</v>
       </c>
       <c r="E22" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F22" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>65.38284522638729</v>
+        <v>10.62471234928793</v>
       </c>
       <c r="D23" t="n">
-        <v>65.20928033771415</v>
+        <v>10.59650805487855</v>
       </c>
       <c r="E23" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F23" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1184,16 +1184,16 @@
         <v>23</v>
       </c>
       <c r="C24" t="n">
-        <v>45.69811665417095</v>
+        <v>7.42594395630278</v>
       </c>
       <c r="D24" t="n">
-        <v>45.44222496739781</v>
+        <v>7.384361557202145</v>
       </c>
       <c r="E24" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F24" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1216,16 +1216,16 @@
         <v>24</v>
       </c>
       <c r="C25" t="n">
-        <v>44.96227134442447</v>
+        <v>7.306369093468977</v>
       </c>
       <c r="D25" t="n">
-        <v>44.6492810907766</v>
+        <v>7.255508177251198</v>
       </c>
       <c r="E25" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F25" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1248,16 +1248,16 @@
         <v>25</v>
       </c>
       <c r="C26" t="n">
-        <v>68.94657596065728</v>
+        <v>11.20381859360681</v>
       </c>
       <c r="D26" t="n">
-        <v>68.72104849642652</v>
+        <v>11.16717038066931</v>
       </c>
       <c r="E26" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F26" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1280,16 +1280,16 @@
         <v>26</v>
       </c>
       <c r="C27" t="n">
-        <v>60.54627903422827</v>
+        <v>9.838770343062095</v>
       </c>
       <c r="D27" t="n">
-        <v>60.25013967958422</v>
+        <v>9.790647697932435</v>
       </c>
       <c r="E27" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F27" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1312,16 +1312,16 @@
         <v>27</v>
       </c>
       <c r="C28" t="n">
-        <v>38.48345284238166</v>
+        <v>6.25356108688702</v>
       </c>
       <c r="D28" t="n">
-        <v>38.20297517053401</v>
+        <v>6.207983465211777</v>
       </c>
       <c r="E28" t="n">
-        <v>16.25837087782054</v>
+        <v>2.641985267645839</v>
       </c>
       <c r="F28" t="n">
-        <v>16.27734277328756</v>
+        <v>2.645068200659229</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
